--- a/Piaui/2026/Julho/Dados/gabarito_2serie_lp 3ª SIMULA.xlsx
+++ b/Piaui/2026/Julho/Dados/gabarito_2serie_lp 3ª SIMULA.xlsx
@@ -9,7 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="LP_2EM" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="LP_2EM_S3" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
